--- a/lab1/Results_lab1_p1.xlsx
+++ b/lab1/Results_lab1_p1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chern\python\MPiAA\Lab1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chern\python\MPiAA\Lab1\lab1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CABB296E-3219-477D-B044-65FC4EFD6D73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93D15AC6-1CD5-4C29-8E6C-2D5C6B06FFB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="26">
   <si>
     <t>Время</t>
   </si>
@@ -94,9 +94,6 @@
   </si>
   <si>
     <t>m</t>
-  </si>
-  <si>
-    <t>Сложность</t>
   </si>
   <si>
     <r>
@@ -127,7 +124,7 @@
     <t>O(n)</t>
   </si>
   <si>
-    <t>O(m ∙ n)</t>
+    <t>Теоретическая временная сложность</t>
   </si>
 </sst>
 </file>
@@ -345,99 +342,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>923925</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>229095</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>28833</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Рисунок 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3B1C149B-2789-6BFD-6DF7-DD60788A674D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10096500" y="3152775"/>
-          <a:ext cx="3543795" cy="1848108"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>904875</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>38486</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>124225</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Рисунок 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DAF003CC-3D38-B062-6DCA-65A749FD8A3F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10077450" y="114300"/>
-          <a:ext cx="2762636" cy="2867425"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -711,8 +615,8 @@
     <col min="3" max="3" width="11" style="3" customWidth="1"/>
     <col min="4" max="4" width="16.6640625" style="3" customWidth="1"/>
     <col min="5" max="5" width="32.6640625" style="3" customWidth="1"/>
-    <col min="6" max="6" width="17.33203125" style="3" customWidth="1"/>
-    <col min="7" max="7" width="17.88671875" style="3" customWidth="1"/>
+    <col min="6" max="6" width="52.6640625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="9.21875" style="3" customWidth="1"/>
     <col min="8" max="16384" width="9.109375" style="3"/>
   </cols>
   <sheetData>
@@ -733,7 +637,7 @@
         <v>0</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G1" s="1"/>
       <c r="H1" s="2"/>
@@ -756,7 +660,7 @@
         <v>9</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -829,7 +733,7 @@
         <v>9</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
@@ -912,7 +816,7 @@
         <v>15</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
@@ -997,7 +901,7 @@
         <v>9</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
@@ -1142,6 +1046,5 @@
     <mergeCell ref="B2:B5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>